--- a/examples/wangetal2018/out/ResultFiles/AC_0.2_nfc.xlsx
+++ b/examples/wangetal2018/out/ResultFiles/AC_0.2_nfc.xlsx
@@ -14,17 +14,18 @@
     <sheet name="Compressor design" sheetId="5" r:id="rId5"/>
     <sheet name="Pressure profile" sheetId="6" r:id="rId6"/>
     <sheet name="Demand error" sheetId="7" r:id="rId7"/>
+    <sheet name="ProFAST" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="339">
   <si>
     <t xml:space="preserve">
 ---------DISCLAIMER---------
-AS NOTED IN THE LICENSE, ALLIANCE FOR SUSTAINABLE ENERGY, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
+AS NOTED IN THE LICENSE, ALLIANCE FOR ENERGY INNOVATION, LLC: (i) DISCLAIMS ANY WARRANTIES, EXPRESS OR IMPLIED, INCLUDING BUT NOT LIMITED TO ANY IMPLIED WARRANTIES OF MERCHANTABILITY, FITNESS FOR A PARTICULAR PURPOSE, TITLE OR NON-INFRINGEMENT, AND (ii) DOES NOT ASSUME ANY LEGAL LIABILITY OR RESPONSIBILITY FOR THE ACCURACY, COMPLETENESS, OR USEFULNESS OF SOFTWARE OR ITS OUTPUTS. ANY RELIANCE BY THE USER ON THE SOFTWARE IS DONE AT THE USER’S OWN RISK.
 BlendPATH was developed to provide the user with economic analytical capabilities to evaluate potential natural gas transmission pipeline modifications for accommodating hydrogen blending or pure hydrogen streams and to assess the potential associated economic impacts. This model is intended for use during the early stages of pipeline repurposing concept evaluation, which is defined here as the initial project phase when the developer has already gathered the relevant pipeline material design and operation data but has not yet conducted the detailed pipeline materials testing, as specified in ASME B31.12, or performed the in-line inspections that qualify a given pipeline section for hydrogen or hydrogen blending service. Despite BlendPATH using ASME B31.12 to assess existing natural gas transmission pipelines and establish potential pipeline modifications for a natural gas transmission pipeline network to meet ASME B31.12 design requirements, BlendPATH does not qualify the examined pipeline network or modifications thereof for pure hydrogen or hydrogen blending. Pipeline owners and operators must conduct additional evaluations as specified in ASME B31.12 and other relevant code and regulations, independent of BlendPATH application, to qualify actual natural gas transmission pipelines for operation with hydrogen. Failure to do so may result in pipeline fatigue and/or rupture. It is the sole responsibility of the pipeline owner and operator to ensure that their pipeline qualifies for the ASME B31.12 design option that they choose, and any other relevant code and regulations, and that any defects present in the pipeline are acceptable at the operating pressure chosen.
 ----------------------------
 </t>
@@ -39,12 +40,21 @@
     <t>Network name</t>
   </si>
   <si>
+    <t>examples/wangetal2018</t>
+  </si>
+  <si>
     <t>Save directory</t>
   </si>
   <si>
+    <t>out</t>
+  </si>
+  <si>
     <t>Design option - original</t>
   </si>
   <si>
+    <t>nfc</t>
+  </si>
+  <si>
     <t>Location class</t>
   </si>
   <si>
@@ -57,6 +67,9 @@
     <t>Compression ratio</t>
   </si>
   <si>
+    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
+  </si>
+  <si>
     <t>Blending ratio</t>
   </si>
   <si>
@@ -75,18 +88,27 @@
     <t>Region</t>
   </si>
   <si>
+    <t>GP</t>
+  </si>
+  <si>
     <t>Modification method</t>
   </si>
   <si>
+    <t>ac</t>
+  </si>
+  <si>
     <t>Modification design option</t>
   </si>
   <si>
-    <t>Verbose</t>
+    <t>b</t>
   </si>
   <si>
     <t>Equation of state</t>
   </si>
   <si>
+    <t>rk</t>
+  </si>
+  <si>
     <t>Inline inspection inspection interval</t>
   </si>
   <si>
@@ -111,28 +133,40 @@
     <t>New electric compressor driver efficiency</t>
   </si>
   <si>
-    <t>examples/wangetal2018</t>
-  </si>
-  <si>
-    <t>out</t>
-  </si>
-  <si>
-    <t>nfc</t>
-  </si>
-  <si>
-    <t>[1.2, 1.4, 1.6, 1.8, 2.0]</t>
-  </si>
-  <si>
-    <t>GP</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>rk</t>
+    <t>Pipe price markup</t>
+  </si>
+  <si>
+    <t>Compressor price markup</t>
+  </si>
+  <si>
+    <t>Financial overrides</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Filename suffix</t>
+  </si>
+  <si>
+    <t>Thermodynamic curvefits enabled</t>
+  </si>
+  <si>
+    <t>Composition tracking enabled</t>
+  </si>
+  <si>
+    <t>Scenario type</t>
+  </si>
+  <si>
+    <t>transmission</t>
+  </si>
+  <si>
+    <t>Polymer cost type</t>
+  </si>
+  <si>
+    <t>socal</t>
+  </si>
+  <si>
+    <t>Max velocity allowed in distribution networks</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -144,6 +178,9 @@
     <t>LCOT: Levelized cost of transport</t>
   </si>
   <si>
+    <t>$/MMBTU</t>
+  </si>
+  <si>
     <t>LCOT: New pipe CapEx</t>
   </si>
   <si>
@@ -180,6 +217,12 @@
     <t>LCOT: Supply commpressor fuel</t>
   </si>
   <si>
+    <t>LCOT: Meter set assembly</t>
+  </si>
+  <si>
+    <t>LCOT: Gas pressure regulation and metering station</t>
+  </si>
+  <si>
     <t>LCOT: Fixed O&amp;M</t>
   </si>
   <si>
@@ -192,6 +235,9 @@
     <t>Hydrogen injection price</t>
   </si>
   <si>
+    <t>$/kg</t>
+  </si>
+  <si>
     <t>Natural gas price</t>
   </si>
   <si>
@@ -201,27 +247,48 @@
     <t>Pipeline capacity (daily)</t>
   </si>
   <si>
+    <t>MMBTU/day</t>
+  </si>
+  <si>
     <t>Pipeline capacity (hour)</t>
   </si>
   <si>
+    <t>MMBTU/hr</t>
+  </si>
+  <si>
     <t>Added pipeline</t>
   </si>
   <si>
+    <t>km</t>
+  </si>
+  <si>
+    <t>mi</t>
+  </si>
+  <si>
     <t>Added compressor stations</t>
   </si>
   <si>
     <t>Added compressor capacity</t>
   </si>
   <si>
+    <t>hp</t>
+  </si>
+  <si>
     <t>Compressor fuel usage</t>
   </si>
   <si>
     <t>Compressor fuel usage (electric)</t>
   </si>
   <si>
+    <t>kW</t>
+  </si>
+  <si>
     <t>New pipe</t>
   </si>
   <si>
+    <t>$</t>
+  </si>
+  <si>
     <t>New compressor stations</t>
   </si>
   <si>
@@ -234,39 +301,30 @@
     <t>Valve modifications</t>
   </si>
   <si>
+    <t>Meter set assembly</t>
+  </si>
+  <si>
+    <t>Gas pressure regulating metering station</t>
+  </si>
+  <si>
     <t>Hydrogen energy ratio</t>
   </si>
   <si>
-    <t>$/MMBTU</t>
-  </si>
-  <si>
-    <t>$/kg</t>
-  </si>
-  <si>
-    <t>MMBTU/day</t>
-  </si>
-  <si>
-    <t>MMBTU/hr</t>
-  </si>
-  <si>
-    <t>km</t>
-  </si>
-  <si>
-    <t>mi</t>
-  </si>
-  <si>
-    <t>hp</t>
-  </si>
-  <si>
-    <t>kW</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
+    <t>Emissions intensity (total)</t>
+  </si>
+  <si>
+    <t>kgCO2e/MMBTU</t>
+  </si>
+  <si>
+    <t>Total emissions (annual)</t>
+  </si>
+  <si>
+    <t>MMTCO2e/yr</t>
+  </si>
+  <si>
     <t>Breakdown of original pipe by diameter, schedule and grade</t>
   </si>
   <si>
@@ -282,6 +340,9 @@
     <t>Schedule</t>
   </si>
   <si>
+    <t>Polymer</t>
+  </si>
+  <si>
     <t>X60</t>
   </si>
   <si>
@@ -336,9 +397,6 @@
     <t>C_0_0</t>
   </si>
   <si>
-    <t>C_0_1</t>
-  </si>
-  <si>
     <t>CS1</t>
   </si>
   <si>
@@ -351,9 +409,6 @@
     <t>C_1_2</t>
   </si>
   <si>
-    <t>C_1_3</t>
-  </si>
-  <si>
     <t>CS2</t>
   </si>
   <si>
@@ -417,228 +472,210 @@
     <t>PI01_0</t>
   </si>
   <si>
-    <t>PI01_1_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>PI01_1_remaining</t>
-  </si>
-  <si>
-    <t>PI01</t>
-  </si>
-  <si>
-    <t>PI02_0_pre_C_0_1</t>
-  </si>
-  <si>
-    <t>PI02_0_remaining</t>
+    <t>N01</t>
+  </si>
+  <si>
+    <t>N01_0</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
+    <t>PI01_1</t>
+  </si>
+  <si>
+    <t>N01_1</t>
+  </si>
+  <si>
+    <t>PI01_pre_C_0_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_0_0</t>
+  </si>
+  <si>
+    <t>PI01_remaining</t>
+  </si>
+  <si>
+    <t>N_post_C_0_0</t>
+  </si>
+  <si>
+    <t>N02</t>
+  </si>
+  <si>
+    <t>PI02_0</t>
+  </si>
+  <si>
+    <t>N02_0</t>
   </si>
   <si>
     <t>PI02</t>
   </si>
   <si>
+    <t>N03</t>
+  </si>
+  <si>
     <t>PI03_0</t>
   </si>
   <si>
-    <t>PI03_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>PI03_remaining</t>
-  </si>
-  <si>
-    <t>PI04_0</t>
-  </si>
-  <si>
-    <t>PI04_1_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>PI04_1_remaining</t>
-  </si>
-  <si>
-    <t>PI04_pre_C_1_2</t>
+    <t>N03_C</t>
+  </si>
+  <si>
+    <t>N03_C_0</t>
+  </si>
+  <si>
+    <t>PI03</t>
+  </si>
+  <si>
+    <t>N04</t>
+  </si>
+  <si>
+    <t>PI04_0_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_0</t>
+  </si>
+  <si>
+    <t>PI04_0_remaining</t>
+  </si>
+  <si>
+    <t>N_post_C_1_0</t>
+  </si>
+  <si>
+    <t>N04_0</t>
+  </si>
+  <si>
+    <t>PI04_1</t>
+  </si>
+  <si>
+    <t>N04_1</t>
+  </si>
+  <si>
+    <t>PI04_pre_C_1_1</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_1</t>
   </si>
   <si>
     <t>PI04_remaining</t>
   </si>
   <si>
+    <t>N_post_C_1_1</t>
+  </si>
+  <si>
+    <t>N05</t>
+  </si>
+  <si>
     <t>PI05_0</t>
   </si>
   <si>
-    <t>PI05_1_pre_C_1_3</t>
+    <t>N05_0</t>
+  </si>
+  <si>
+    <t>PI05_1_pre_C_1_2</t>
+  </si>
+  <si>
+    <t>N_pre_C_1_2</t>
   </si>
   <si>
     <t>PI05_1_remaining</t>
   </si>
   <si>
+    <t>N_post_C_1_2</t>
+  </si>
+  <si>
+    <t>N05_1</t>
+  </si>
+  <si>
     <t>PI05</t>
   </si>
   <si>
+    <t>N06</t>
+  </si>
+  <si>
     <t>PI06_0</t>
   </si>
   <si>
+    <t>N06_C</t>
+  </si>
+  <si>
+    <t>N06_C_0</t>
+  </si>
+  <si>
     <t>PI06_1</t>
   </si>
   <si>
+    <t>N06_C_1</t>
+  </si>
+  <si>
     <t>PI06</t>
   </si>
   <si>
+    <t>N_pre_C_2_0</t>
+  </si>
+  <si>
     <t>PI07_0_remaining</t>
   </si>
   <si>
+    <t>N07</t>
+  </si>
+  <si>
+    <t>N07_0</t>
+  </si>
+  <si>
     <t>PI07_1</t>
   </si>
   <si>
+    <t>N07_1</t>
+  </si>
+  <si>
     <t>PI07</t>
   </si>
   <si>
+    <t>N08</t>
+  </si>
+  <si>
     <t>PI08_0</t>
   </si>
   <si>
+    <t>N08_C</t>
+  </si>
+  <si>
+    <t>N08_C_0</t>
+  </si>
+  <si>
     <t>PI08_1</t>
   </si>
   <si>
+    <t>N08_C_1</t>
+  </si>
+  <si>
     <t>PI08</t>
   </si>
   <si>
+    <t>N_pre_C_3_0</t>
+  </si>
+  <si>
     <t>PI09_0_remaining</t>
   </si>
   <si>
+    <t>N09</t>
+  </si>
+  <si>
+    <t>N09_0</t>
+  </si>
+  <si>
     <t>PI09_1</t>
   </si>
   <si>
+    <t>N09_1</t>
+  </si>
+  <si>
     <t>PI09</t>
   </si>
   <si>
-    <t>N01</t>
-  </si>
-  <si>
-    <t>N01_0</t>
-  </si>
-  <si>
-    <t>N_post_C_0_0</t>
-  </si>
-  <si>
-    <t>N01_1</t>
-  </si>
-  <si>
-    <t>N02</t>
-  </si>
-  <si>
-    <t>N_post_C_0_1</t>
-  </si>
-  <si>
-    <t>N02_0</t>
-  </si>
-  <si>
-    <t>N03_C</t>
-  </si>
-  <si>
-    <t>N03_C_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_0</t>
-  </si>
-  <si>
-    <t>N04</t>
-  </si>
-  <si>
-    <t>N04_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_1</t>
-  </si>
-  <si>
-    <t>N04_1</t>
-  </si>
-  <si>
-    <t>N_post_C_1_2</t>
-  </si>
-  <si>
-    <t>N05</t>
-  </si>
-  <si>
-    <t>N05_0</t>
-  </si>
-  <si>
-    <t>N_post_C_1_3</t>
-  </si>
-  <si>
-    <t>N05_1</t>
-  </si>
-  <si>
-    <t>N06_C</t>
-  </si>
-  <si>
-    <t>N06_C_0</t>
-  </si>
-  <si>
-    <t>N06_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_2_0</t>
-  </si>
-  <si>
-    <t>N07_0</t>
-  </si>
-  <si>
-    <t>N07_1</t>
-  </si>
-  <si>
-    <t>N08_C</t>
-  </si>
-  <si>
-    <t>N08_C_0</t>
-  </si>
-  <si>
-    <t>N08_C_1</t>
-  </si>
-  <si>
-    <t>N_post_C_3_0</t>
-  </si>
-  <si>
-    <t>N09_0</t>
-  </si>
-  <si>
-    <t>N09_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_0_1</t>
-  </si>
-  <si>
-    <t>N03</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_0</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_1</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_2</t>
-  </si>
-  <si>
-    <t>N_pre_C_1_3</t>
-  </si>
-  <si>
-    <t>N06</t>
-  </si>
-  <si>
-    <t>N07</t>
-  </si>
-  <si>
-    <t>N08</t>
-  </si>
-  <si>
-    <t>N09</t>
-  </si>
-  <si>
     <t>N10</t>
   </si>
   <si>
-    <t>Existing</t>
-  </si>
-  <si>
     <t>Segment</t>
   </si>
   <si>
@@ -706,22 +743,316 @@
   </si>
   <si>
     <t>N13</t>
+  </si>
+  <si>
+    <t>capacity</t>
+  </si>
+  <si>
+    <t>527617.1846909181</t>
+  </si>
+  <si>
+    <t>long term utilization</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>demand rampup</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>analysis start year</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>operating life</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>installation months</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>TOPC</t>
+  </si>
+  <si>
+    <t>unit price</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
+    <t>decay</t>
+  </si>
+  <si>
+    <t>support utilization</t>
+  </si>
+  <si>
+    <t>sunset years</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Natural Gas-H2 Blend</t>
+  </si>
+  <si>
+    <t>unit</t>
+  </si>
+  <si>
+    <t>MMBTU</t>
+  </si>
+  <si>
+    <t>initial price</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>escalation</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>annual operating incentive</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>taxable</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>incidental revenue</t>
+  </si>
+  <si>
+    <t>credit card fees</t>
+  </si>
+  <si>
+    <t>sales tax</t>
+  </si>
+  <si>
+    <t>road tax</t>
+  </si>
+  <si>
+    <t>labor</t>
+  </si>
+  <si>
+    <t>rate</t>
+  </si>
+  <si>
+    <t>maintenance</t>
+  </si>
+  <si>
+    <t>rent</t>
+  </si>
+  <si>
+    <t>license and permit</t>
+  </si>
+  <si>
+    <t>non depr assets</t>
+  </si>
+  <si>
+    <t>end of proj sale non depr assets</t>
+  </si>
+  <si>
+    <t>installation cost</t>
+  </si>
+  <si>
+    <t>depr type</t>
+  </si>
+  <si>
+    <t>Straight line</t>
+  </si>
+  <si>
+    <t>depr period</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>depreciable</t>
+  </si>
+  <si>
+    <t>one time cap inct</t>
+  </si>
+  <si>
+    <t>MACRS</t>
+  </si>
+  <si>
+    <t>property tax and insurance</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>admin expense</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>tax loss carry forward years</t>
+  </si>
+  <si>
+    <t>capital gains tax rate</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>tax losses monetized</t>
+  </si>
+  <si>
+    <t>sell undepreciated cap</t>
+  </si>
+  <si>
+    <t>loan period if used</t>
+  </si>
+  <si>
+    <t>debt equity ratio of initial financing</t>
+  </si>
+  <si>
+    <t>0.62</t>
+  </si>
+  <si>
+    <t>debt interest rate</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>debt type</t>
+  </si>
+  <si>
+    <t>Revolving debt</t>
+  </si>
+  <si>
+    <t>total income tax rate</t>
+  </si>
+  <si>
+    <t>0.2574</t>
+  </si>
+  <si>
+    <t>cash onhand</t>
+  </si>
+  <si>
+    <t>general inflation rate</t>
+  </si>
+  <si>
+    <t>leverage after tax nominal discount rate</t>
+  </si>
+  <si>
+    <t>0.13</t>
+  </si>
+  <si>
+    <t>fraction of year operated</t>
+  </si>
+  <si>
+    <t>[0. 0. 0. 0. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1. 1.
+ 1. 1. 1. 1. 1. 1.]</t>
+  </si>
+  <si>
+    <t>New pipe CapEx</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>depr_type</t>
+  </si>
+  <si>
+    <t>depr_period</t>
+  </si>
+  <si>
+    <t>refurb</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>New compression capacity CapEx</t>
+  </si>
+  <si>
+    <t>84718748.848876</t>
+  </si>
+  <si>
+    <t>Refurbished compressor capacity CapEx</t>
+  </si>
+  <si>
+    <t>50748077.07023712</t>
+  </si>
+  <si>
+    <t>Supply compressor CapEx</t>
+  </si>
+  <si>
+    <t>Meter &amp; regulator station modification CapEx</t>
+  </si>
+  <si>
+    <t>10486757.29473448</t>
+  </si>
+  <si>
+    <t>Valve replacement CapEx</t>
+  </si>
+  <si>
+    <t>24862120.0</t>
+  </si>
+  <si>
+    <t>Original network residual value</t>
+  </si>
+  <si>
+    <t>Gas pressure regulation and metering station</t>
+  </si>
+  <si>
+    <t>Compressor fuel</t>
+  </si>
+  <si>
+    <t>{'2048': np.float64(18.51020451680288), '2049': np.float64(18.972959629722947), '2050': np.float64(19.447283620466017), '2051': np.float64(19.933465710977668), '2052': np.float64(20.431802353752108), '2053': np.float64(20.94259741259591), '2054': np.float64(21.466162347910803), '2055': np.float64(22.002816406608567), '2056': np.float64(22.552886816773782), '2057': np.float64(23.116708987193125), '2058': np.float64(23.694626711872953), '2059': np.float64(24.286992379669773), '2060': np.float64(24.894167189161518), '2061': np.float64(25.516521368890555), '2062': np.float64(26.154434403112816), '2063': np.float64(26.808295263190633), '2064': np.float64(27.478502644770398), '2065': np.float64(28.165465210889653), '2066': np.float64(28.869601841161888), '2067': np.float64(29.591341887190936), '2068': np.float64(30.331125434370712), '2069': np.float64(31.089403570229972), '2070': np.float64(31.866638659485716), '2071': np.float64(32.663304625972856), '2072': np.float64(33.47988724162218), '2073': np.float64(34.31688442266273), '2074': np.float64(35.174806533229294), '2075': np.float64(36.05417669656002), '2076': np.float64(36.95553111397402), '2077': np.float64(37.87941939182336), '2078': np.float64(38.82640487661895), '2079': np.float64(39.79706499853442), '2080': np.float64(40.79199162349778), '2081': np.float64(41.81179141408522), '2082': np.float64(42.85708619943734), '2020': np.float64(9.271350212696891), '2021': np.float64(9.503133968014312), '2022': np.float64(9.740712317214669), '2023': np.float64(9.984230125145036), '2024': np.float64(10.23383587827366), '2025': np.float64(10.4896817752305), '2026': np.float64(10.75192381961126), '2027': np.float64(11.020721915101543), '2028': np.float64(11.29623996297908), '2029': np.float64(11.578645962053557), '2030': np.float64(11.868112111104894), '2031': np.float64(12.164814913882516), '2032': np.float64(12.468935286729579), '2033': np.float64(12.780658668897814), '2034': np.float64(13.100175135620262), '2035': np.float64(13.427679514010764), '2036': np.float64(13.763371501861034), '2037': np.float64(14.107455789407558), '2038': np.float64(14.460142184142745), '2039': np.float64(14.821645738746312), '2040': np.float64(15.192186882214969), '2041': np.float64(15.571991554270344), '2042': np.float64(15.9612913431271), '2043': np.float64(16.360323626705277), '2044': np.float64(16.769331717372904), '2045': np.float64(17.18856501030723), '2046': np.float64(17.618279135564904), '2047': np.float64(18.058736113954026)}</t>
+  </si>
+  <si>
+    <t>usage</t>
+  </si>
+  <si>
+    <t>0.02021135789793954</t>
+  </si>
+  <si>
+    <t>Compressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel (electric)</t>
+  </si>
+  <si>
+    <t>Supply commpressor fuel</t>
+  </si>
+  <si>
+    <t>In-line inspection</t>
+  </si>
+  <si>
+    <t>3277333.333333336</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -737,7 +1068,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -745,32 +1076,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1084,14 +1397,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1100,28 +1413,28 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1129,7 +1442,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1137,7 +1450,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1145,15 +1458,15 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B9">
         <v>0.2</v>
@@ -1161,7 +1474,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>7.39</v>
@@ -1169,7 +1482,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>4.40756</v>
@@ -1177,7 +1490,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12">
         <v>0.07000000000000001</v>
@@ -1185,7 +1498,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3.325</v>
@@ -1193,63 +1506,63 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
+        <v>29</v>
+      </c>
+      <c r="B20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B21" t="b">
         <v>0</v>
@@ -1257,39 +1570,100 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="b">
-        <v>0</v>
+        <v>31</v>
+      </c>
+      <c r="B22">
+        <v>0.78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B23">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>0.88</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25">
-        <v>0.357</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>35</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1299,268 +1673,268 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>37</v>
+      <c r="C1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="B2">
-        <v>0.3669336563873711</v>
+        <v>0.3471251320076941</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B4">
-        <v>0.06519129667489668</v>
+        <v>0.05327798237909378</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B5">
-        <v>0.03179962138373985</v>
+        <v>0.0319144840151503</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B7">
-        <v>0.00657118320077798</v>
+        <v>0.006594918810231102</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B8">
-        <v>0.01557903369822032</v>
+        <v>0.01563530634322498</v>
       </c>
       <c r="C8" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B10">
         <v>0.01701801172198348</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="B11">
-        <v>0.1918832502923665</v>
+        <v>0.1873865773459548</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B15">
-        <v>0.004666732847432012</v>
+        <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B16">
-        <v>0.03265772506014108</v>
+        <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B17">
-        <v>0.001566801507813138</v>
+        <v>0.004279944705625635</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B18">
-        <v>4.40756</v>
+        <v>0.02950880182794798</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B19">
-        <v>7.39</v>
+        <v>0.001509104858481968</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B20">
-        <v>9.271350212696891</v>
+        <v>4.40756</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B21">
-        <v>527617.1846909181</v>
+        <v>7.39</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B22">
-        <v>21984.04936212159</v>
+        <v>9.271350212696891</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>527617.1846909181</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>21984.04936212159</v>
       </c>
       <c r="C24" t="s">
         <v>75</v>
@@ -1568,472 +1942,307 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B26">
-        <v>46271.03677623437</v>
+        <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="B27">
-        <v>10919.75796254079</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B28">
-        <v>454.9899151058661</v>
+        <v>40726.09983424746</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>10663.85975289141</v>
       </c>
       <c r="C29" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>444.3274897038089</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B31">
-        <v>104036865.975329</v>
+        <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33">
+        <v>84718748.848876</v>
+      </c>
+      <c r="C33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>88</v>
+      </c>
+      <c r="B34">
         <v>50748077.07023712</v>
       </c>
-      <c r="C32" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33">
+      <c r="C34" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35">
         <v>10486757.29473448</v>
       </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>68</v>
-      </c>
-      <c r="B34">
+      <c r="C35" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36">
         <v>24862120</v>
       </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35">
+      <c r="C36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>91</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39">
         <v>7.406825856025969</v>
       </c>
-      <c r="C35" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
-      <c r="A39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
-      <c r="A41">
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40">
+        <v>59.96789061074948</v>
+      </c>
+      <c r="C40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41">
+        <v>11.54863270980225</v>
+      </c>
+      <c r="C41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>100</v>
+      </c>
+      <c r="B47" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
         <v>650</v>
       </c>
-      <c r="B41">
+      <c r="B48">
         <v>400.0000000000002</v>
       </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="A45" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52">
-        <v>4.620898857823486</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>6196.717786318451</v>
-      </c>
-      <c r="E52">
-        <v>13447784.74391999</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>44.16554452507287</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
+      <c r="C48" t="s">
+        <v>105</v>
+      </c>
+      <c r="D48" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53">
-        <v>4.589017185282112</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53">
-        <v>6153.963825807017</v>
-      </c>
-      <c r="E53">
-        <v>13400466.03344767</v>
-      </c>
-      <c r="F53">
-        <v>0</v>
-      </c>
-      <c r="G53">
-        <v>43.86082644500153</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54">
-        <v>4.557128663762801</v>
-      </c>
-      <c r="C54">
-        <v>12.5</v>
-      </c>
-      <c r="D54">
-        <v>0</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G54">
-        <v>43.55604290389126</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55">
-        <v>5.199619060371232</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-      <c r="D55">
-        <v>6972.793152339029</v>
-      </c>
-      <c r="E55">
-        <v>14309488.92802266</v>
-      </c>
-      <c r="F55">
-        <v>0</v>
-      </c>
-      <c r="G55">
-        <v>49.69682613490681</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56">
-        <v>2.972032942295563</v>
-      </c>
-      <c r="C56">
-        <v>0</v>
-      </c>
-      <c r="D56">
-        <v>3985.555616277196</v>
-      </c>
-      <c r="E56">
-        <v>11021433.00223319</v>
-      </c>
-      <c r="F56">
-        <v>0</v>
-      </c>
-      <c r="G56">
-        <v>28.40604334386236</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" t="s">
-        <v>107</v>
-      </c>
-      <c r="B57">
-        <v>2.660389197684499</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-      <c r="D57">
-        <v>3567.635121878867</v>
-      </c>
-      <c r="E57">
-        <v>10567628.10021256</v>
-      </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57">
-        <v>25.42742033087925</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" t="s">
         <v>108</v>
       </c>
-      <c r="B58">
-        <v>2.64858849206394</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>3551.810139627585</v>
-      </c>
-      <c r="E58">
-        <v>10550474.22654086</v>
-      </c>
-      <c r="F58">
-        <v>0</v>
-      </c>
-      <c r="G58">
-        <v>25.31463175758476</v>
-      </c>
-      <c r="H58">
-        <v>0</v>
+      <c r="D54" t="s">
+        <v>103</v>
+      </c>
+      <c r="E54" t="s">
+        <v>109</v>
+      </c>
+      <c r="F54" t="s">
+        <v>110</v>
+      </c>
+      <c r="G54" t="s">
+        <v>111</v>
+      </c>
+      <c r="H54" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>109</v>
-      </c>
-      <c r="B59">
-        <v>2.636765853031398</v>
-      </c>
-      <c r="C59">
-        <v>12.5</v>
-      </c>
-      <c r="D59">
-        <v>0</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="G59">
-        <v>25.20163354951717</v>
-      </c>
-      <c r="H59">
-        <v>0</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>110</v>
-      </c>
-      <c r="B60">
-        <v>5.97826501473844</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-      <c r="D60">
-        <v>8016.972950064543</v>
-      </c>
-      <c r="E60">
-        <v>15477160.67336135</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
-      <c r="G60">
-        <v>57.13895452268778</v>
-      </c>
-      <c r="H60">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" t="s">
+        <v>116</v>
+      </c>
+      <c r="D60" t="s">
+        <v>117</v>
+      </c>
+      <c r="E60" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" t="s">
+        <v>119</v>
+      </c>
+      <c r="G60" t="s">
+        <v>120</v>
+      </c>
+      <c r="H60" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B61">
-        <v>5.905876802758123</v>
+        <v>7.417399501826221</v>
       </c>
       <c r="C61">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>9946.881079938999</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>17660322.29479652</v>
       </c>
       <c r="F61">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>56.44708376384304</v>
+        <v>70.89388840517942</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2041,27 +2250,209 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B62">
-        <v>5.83554919682159</v>
+        <v>7.328867592105301</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D62">
-        <v>7825.588183921689</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>15262430.26759074</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="G62">
-        <v>55.77490782861931</v>
+        <v>70.04771970056713</v>
       </c>
       <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63">
+        <v>5.314134003317778</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>7126.359981129207</v>
+      </c>
+      <c r="E63">
+        <v>14480621.70552986</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>50.79133501015063</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64">
+        <v>3.282122788091933</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>4401.392301287044</v>
+      </c>
+      <c r="E64">
+        <v>11474485.84564348</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>31.36981453052349</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65">
+        <v>3.263213303473446</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>4376.034304223961</v>
+      </c>
+      <c r="E65">
+        <v>11446815.23847485</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>31.18908179636074</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>127</v>
+      </c>
+      <c r="B66">
+        <v>3.244505271756164</v>
+      </c>
+      <c r="C66">
+        <v>12.5</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G66">
+        <v>31.01027450513704</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>128</v>
+      </c>
+      <c r="B67">
+        <v>5.606570002645178</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>7518.522504947236</v>
+      </c>
+      <c r="E67">
+        <v>14918574.77541785</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>53.58637457851545</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68">
+        <v>5.545688391904807</v>
+      </c>
+      <c r="C68">
+        <v>12.5</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>16916025.69007904</v>
+      </c>
+      <c r="G68">
+        <v>53.00448140737202</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>130</v>
+      </c>
+      <c r="B69">
+        <v>5.486055139163487</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>7356.909662721019</v>
+      </c>
+      <c r="E69">
+        <v>14737928.98901344</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>52.434519770003</v>
+      </c>
+      <c r="H69">
         <v>0</v>
       </c>
     </row>
@@ -2072,63 +2463,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R32"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>128</v>
+      <c r="A1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I1" t="s">
+        <v>138</v>
+      </c>
+      <c r="J1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K1" t="s">
+        <v>140</v>
+      </c>
+      <c r="L1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" t="s">
+        <v>141</v>
+      </c>
+      <c r="N1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P1" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>145</v>
+      </c>
+      <c r="R1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -2136,31 +2527,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F2">
-        <v>113.0922305504194</v>
+        <v>113.0391218025007</v>
       </c>
       <c r="G2">
         <v>650</v>
       </c>
       <c r="H2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I2">
         <v>9.525</v>
       </c>
       <c r="J2" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K2">
         <v>4.865822962046021</v>
@@ -2175,16 +2566,16 @@
         <v>4865822.962046022</v>
       </c>
       <c r="O2">
-        <v>4427462.918581173</v>
+        <v>4438116.177952614</v>
       </c>
       <c r="P2">
-        <v>12.47766632642912</v>
+        <v>13.28030091842816</v>
       </c>
       <c r="Q2">
-        <v>0.02516059761349215</v>
+        <v>0.02709473465274957</v>
       </c>
       <c r="R2">
-        <v>24.07718013670485</v>
+        <v>23.76596548511066</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -2192,55 +2583,55 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="E3" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F3">
-        <v>113.092224907112</v>
+        <v>113.0391217837879</v>
       </c>
       <c r="G3">
         <v>650</v>
       </c>
       <c r="H3" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I3">
         <v>9.525</v>
       </c>
       <c r="J3" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K3">
         <v>4.865822962046021</v>
       </c>
       <c r="L3">
-        <v>9.999999999999998</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="M3">
-        <v>6.213709999999999</v>
+        <v>8.284946666666665</v>
       </c>
       <c r="N3">
-        <v>4427462.918581173</v>
+        <v>4438116.177952614</v>
       </c>
       <c r="O3">
-        <v>4066380.087520617</v>
+        <v>3963528.099593595</v>
       </c>
       <c r="P3">
-        <v>12.5009854916184</v>
+        <v>14.89848581868826</v>
       </c>
       <c r="Q3">
-        <v>0.02523955993254112</v>
+        <v>0.03048795613925226</v>
       </c>
       <c r="R3">
-        <v>25.1672636273331</v>
+        <v>25.17228094095296</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -2248,55 +2639,55 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F4">
-        <v>112.8701631804663</v>
+        <v>113.0391209051033</v>
       </c>
       <c r="G4">
         <v>650</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I4">
         <v>9.525</v>
       </c>
       <c r="J4" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K4">
         <v>4.865822962046021</v>
       </c>
       <c r="L4">
-        <v>3.333333333333336</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="M4">
-        <v>2.071236666666668</v>
+        <v>5.178091666666666</v>
       </c>
       <c r="N4">
-        <v>4865822.962046022</v>
+        <v>3963528.099593595</v>
       </c>
       <c r="O4">
-        <v>4760595.472101057</v>
+        <v>3635097.03161606</v>
       </c>
       <c r="P4">
-        <v>12.36359079174688</v>
+        <v>16.26054766228459</v>
       </c>
       <c r="Q4">
-        <v>0.02490051746145235</v>
+        <v>0.03335025322827282</v>
       </c>
       <c r="R4">
-        <v>23.18326960242841</v>
+        <v>26.29778014425714</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -2304,55 +2695,55 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="C5" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F5">
-        <v>112.8701629447994</v>
+        <v>112.6817535681772</v>
       </c>
       <c r="G5">
         <v>650</v>
       </c>
       <c r="H5" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I5">
         <v>9.525</v>
       </c>
       <c r="J5" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K5">
         <v>4.865822962046021</v>
       </c>
       <c r="L5">
-        <v>13.33333333333333</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>8.284946666666665</v>
+        <v>3.106855</v>
       </c>
       <c r="N5">
-        <v>4760595.472101057</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O5">
-        <v>4312888.561809869</v>
+        <v>4711069.308999785</v>
       </c>
       <c r="P5">
-        <v>12.39399417151668</v>
+        <v>12.45574344789795</v>
       </c>
       <c r="Q5">
-        <v>0.02500196871960631</v>
+        <v>0.0253707443538535</v>
       </c>
       <c r="R5">
-        <v>24.40831998517606</v>
+        <v>23.05281262660782</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -2360,55 +2751,55 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F6">
-        <v>112.8701624135459</v>
+        <v>112.6817535641919</v>
       </c>
       <c r="G6">
         <v>650</v>
       </c>
       <c r="H6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I6">
         <v>9.525</v>
       </c>
       <c r="J6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K6">
         <v>4.865822962046021</v>
       </c>
       <c r="L6">
-        <v>6.666666666666664</v>
+        <v>15</v>
       </c>
       <c r="M6">
-        <v>4.142473333333332</v>
+        <v>9.320565</v>
       </c>
       <c r="N6">
-        <v>4312888.561809869</v>
+        <v>4711069.308999785</v>
       </c>
       <c r="O6">
-        <v>4069771.039548116</v>
+        <v>4212053.220545113</v>
       </c>
       <c r="P6">
-        <v>12.40927892005199</v>
+        <v>13.96283782110739</v>
       </c>
       <c r="Q6">
-        <v>0.02505409328594885</v>
+        <v>0.02852664081125121</v>
       </c>
       <c r="R6">
-        <v>25.15637671690195</v>
+        <v>24.40764848137769</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -2416,111 +2807,111 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F7">
-        <v>112.6491392073757</v>
+        <v>112.6817535450376</v>
       </c>
       <c r="G7">
         <v>650</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I7">
         <v>9.525</v>
       </c>
       <c r="J7" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K7">
         <v>4.865822962046021</v>
       </c>
       <c r="L7">
-        <v>8.333333333333336</v>
+        <v>15</v>
       </c>
       <c r="M7">
-        <v>5.178091666666668</v>
+        <v>9.320565</v>
       </c>
       <c r="N7">
-        <v>4865822.962046022</v>
+        <v>4212053.220545113</v>
       </c>
       <c r="O7">
-        <v>4599097.546686064</v>
+        <v>3644078.427078389</v>
       </c>
       <c r="P7">
-        <v>12.38498497092171</v>
+        <v>16.16881344649111</v>
       </c>
       <c r="Q7">
-        <v>0.02495749620331185</v>
+        <v>0.03316000448011889</v>
       </c>
       <c r="R7">
-        <v>23.60528054274031</v>
+        <v>26.26504615284622</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D8" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="E8" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F8">
-        <v>112.6491391812656</v>
+        <v>112.328709622493</v>
       </c>
       <c r="G8">
         <v>650</v>
       </c>
       <c r="H8" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I8">
         <v>9.525</v>
       </c>
       <c r="J8" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K8">
         <v>4.865822962046021</v>
       </c>
       <c r="L8">
-        <v>15</v>
+        <v>15.75</v>
       </c>
       <c r="M8">
-        <v>9.320565</v>
+        <v>9.786593249999999</v>
       </c>
       <c r="N8">
-        <v>4599097.546686064</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O8">
-        <v>4073185.409801771</v>
+        <v>4362643.803546251</v>
       </c>
       <c r="P8">
-        <v>12.41951311406938</v>
+        <v>13.42948490970602</v>
       </c>
       <c r="Q8">
-        <v>0.02507444229395871</v>
+        <v>0.02741188077541113</v>
       </c>
       <c r="R8">
-        <v>25.14542888320394</v>
+        <v>23.97453454961112</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -2528,31 +2919,31 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>165</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E9" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F9">
-        <v>112.4296184240329</v>
+        <v>112.3287096212532</v>
       </c>
       <c r="G9">
         <v>650</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I9">
         <v>9.525</v>
       </c>
       <c r="J9" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K9">
         <v>4.865822962046021</v>
@@ -2564,19 +2955,19 @@
         <v>9.786593249999999</v>
       </c>
       <c r="N9">
-        <v>4865822.962046022</v>
+        <v>4362643.803546251</v>
       </c>
       <c r="O9">
-        <v>4349434.559984447</v>
+        <v>3791934.656830566</v>
       </c>
       <c r="P9">
-        <v>12.42928270913904</v>
+        <v>15.48396751606819</v>
       </c>
       <c r="Q9">
-        <v>0.02507000427135664</v>
+        <v>0.0317221484267555</v>
       </c>
       <c r="R9">
-        <v>24.30121578682969</v>
+        <v>25.74314674744834</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -2584,55 +2975,55 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="C10" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" t="s">
         <v>168</v>
       </c>
-      <c r="D10" t="s">
-        <v>194</v>
-      </c>
       <c r="E10" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F10">
-        <v>112.429618422974</v>
+        <v>92.54305874502482</v>
       </c>
       <c r="G10">
         <v>650</v>
       </c>
       <c r="H10" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I10">
         <v>9.525</v>
       </c>
       <c r="J10" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K10">
         <v>4.865822962046021</v>
       </c>
       <c r="L10">
-        <v>10.25000000000001</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>6.369052750000007</v>
+        <v>0.621371</v>
       </c>
       <c r="N10">
-        <v>4349434.559984447</v>
+        <v>3791934.656830566</v>
       </c>
       <c r="O10">
-        <v>3975854.518199351</v>
+        <v>3765171.838831699</v>
       </c>
       <c r="P10">
-        <v>12.45318816623289</v>
+        <v>12.84811424168087</v>
       </c>
       <c r="Q10">
-        <v>0.02515112645042848</v>
+        <v>0.02632707770163828</v>
       </c>
       <c r="R10">
-        <v>25.463231798922</v>
+        <v>25.8353090739499</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -2640,55 +3031,55 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E11" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F11">
-        <v>112.1791464066949</v>
+        <v>92.28707022347776</v>
       </c>
       <c r="G11">
         <v>650</v>
       </c>
       <c r="H11" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I11">
         <v>9.525</v>
       </c>
       <c r="J11" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K11">
         <v>4.865822962046021</v>
       </c>
       <c r="L11">
-        <v>5.499999999999993</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="M11">
-        <v>3.417540499999995</v>
+        <v>9.424126833333336</v>
       </c>
       <c r="N11">
         <v>4865822.962046022</v>
       </c>
       <c r="O11">
-        <v>4693014.32323207</v>
+        <v>4542771.487687924</v>
       </c>
       <c r="P11">
-        <v>12.3075205174481</v>
+        <v>10.5879211715799</v>
       </c>
       <c r="Q11">
-        <v>0.02479352418062126</v>
+        <v>0.02158756025335964</v>
       </c>
       <c r="R11">
-        <v>23.35709428330448</v>
+        <v>23.48555413701997</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -2696,31 +3087,31 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F12">
-        <v>92.39349554013306</v>
+        <v>92.28707022347248</v>
       </c>
       <c r="G12">
         <v>650</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I12">
         <v>9.525</v>
       </c>
       <c r="J12" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K12">
         <v>4.865822962046021</v>
@@ -2732,19 +3123,19 @@
         <v>10.04549783333334</v>
       </c>
       <c r="N12">
-        <v>4693014.32323207</v>
+        <v>4542771.487687924</v>
       </c>
       <c r="O12">
-        <v>4324128.083916678</v>
+        <v>4170354.630079336</v>
       </c>
       <c r="P12">
-        <v>10.16711865191663</v>
+        <v>11.55172113799232</v>
       </c>
       <c r="Q12">
-        <v>0.02050898486771386</v>
+        <v>0.02360706578460884</v>
       </c>
       <c r="R12">
-        <v>24.37523000222854</v>
+        <v>24.53120096247372</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -2752,55 +3143,55 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D13" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="E13" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F13">
-        <v>92.39349554010131</v>
+        <v>92.28707022344641</v>
       </c>
       <c r="G13">
         <v>650</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I13">
         <v>9.525</v>
       </c>
       <c r="J13" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K13">
         <v>4.865822962046021</v>
       </c>
       <c r="L13">
-        <v>4.333333333333343</v>
+        <v>1.166666666666657</v>
       </c>
       <c r="M13">
-        <v>2.692607666666673</v>
+        <v>0.7249328333333274</v>
       </c>
       <c r="N13">
-        <v>4324128.083916678</v>
+        <v>4170354.630079336</v>
       </c>
       <c r="O13">
-        <v>4219533.033288239</v>
+        <v>4142159.279711842</v>
       </c>
       <c r="P13">
-        <v>10.17529758434373</v>
+        <v>11.63145802819788</v>
       </c>
       <c r="Q13">
-        <v>0.02053257446466895</v>
+        <v>0.02377446788866163</v>
       </c>
       <c r="R13">
-        <v>24.68847610332003</v>
+        <v>24.61571987578913</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2808,55 +3199,55 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D14" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E14" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F14">
-        <v>92.25032903769505</v>
+        <v>92.1289663045834</v>
       </c>
       <c r="G14">
         <v>650</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I14">
         <v>9.525</v>
       </c>
       <c r="J14" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K14">
         <v>4.865822962046021</v>
       </c>
       <c r="L14">
-        <v>11.83333333333333</v>
+        <v>15.00000000000001</v>
       </c>
       <c r="M14">
-        <v>7.352890166666665</v>
+        <v>9.320565000000007</v>
       </c>
       <c r="N14">
         <v>4865822.962046022</v>
       </c>
       <c r="O14">
-        <v>4610217.933448978</v>
+        <v>4547558.708764091</v>
       </c>
       <c r="P14">
-        <v>10.16866213830813</v>
+        <v>10.55845238998954</v>
       </c>
       <c r="Q14">
-        <v>0.02049054186909231</v>
+        <v>0.02152682819096745</v>
       </c>
       <c r="R14">
-        <v>23.57548007896672</v>
+        <v>23.47296360364232</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -2864,55 +3255,55 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D15" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F15">
-        <v>92.25032903769414</v>
+        <v>92.12896630458324</v>
       </c>
       <c r="G15">
         <v>650</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I15">
         <v>9.525</v>
       </c>
       <c r="J15" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K15">
         <v>4.865822962046021</v>
       </c>
       <c r="L15">
-        <v>14.16666666666669</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M15">
-        <v>8.802755833333347</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N15">
-        <v>4610217.933448978</v>
+        <v>4547558.708764091</v>
       </c>
       <c r="O15">
-        <v>4283280.835380175</v>
+        <v>4164881.467165636</v>
       </c>
       <c r="P15">
-        <v>10.19556733607886</v>
+        <v>11.54729721165793</v>
       </c>
       <c r="Q15">
-        <v>0.02056920812632711</v>
+        <v>0.02359888394130034</v>
       </c>
       <c r="R15">
-        <v>24.49613655403926</v>
+        <v>24.54753932535281</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -2920,55 +3311,55 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="C16" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D16" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E16" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F16">
-        <v>92.12217479834551</v>
+        <v>92.12896630458063</v>
       </c>
       <c r="G16">
         <v>650</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I16">
         <v>9.525</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K16">
         <v>4.865822962046021</v>
       </c>
       <c r="L16">
-        <v>1.999999999999986</v>
+        <v>0.8333333333333144</v>
       </c>
       <c r="M16">
-        <v>1.242741999999991</v>
+        <v>0.5178091666666549</v>
       </c>
       <c r="N16">
-        <v>4865822.962046022</v>
+        <v>4164881.467165636</v>
       </c>
       <c r="O16">
-        <v>4823729.897071396</v>
+        <v>4144802.552341937</v>
       </c>
       <c r="P16">
-        <v>10.08102367981056</v>
+        <v>11.60402224223163</v>
       </c>
       <c r="Q16">
-        <v>0.02029868360360829</v>
+        <v>0.02371797381438252</v>
       </c>
       <c r="R16">
-        <v>23.02433988158578</v>
+        <v>24.60775921915323</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -2976,55 +3367,55 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="C17" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D17" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="E17" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F17">
-        <v>92.12217479834548</v>
+        <v>91.97177328206848</v>
       </c>
       <c r="G17">
         <v>650</v>
       </c>
       <c r="H17" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I17">
         <v>9.525</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K17">
         <v>4.865822962046021</v>
       </c>
       <c r="L17">
-        <v>16.66666666666667</v>
+        <v>15.83333333333336</v>
       </c>
       <c r="M17">
-        <v>10.35618333333334</v>
+        <v>9.838374166666684</v>
       </c>
       <c r="N17">
-        <v>4823729.897071396</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O17">
-        <v>4456799.123767665</v>
+        <v>4530373.771127228</v>
       </c>
       <c r="P17">
-        <v>10.11198017345237</v>
+        <v>10.58115225212747</v>
       </c>
       <c r="Q17">
-        <v>0.02038810948780464</v>
+        <v>0.02157544084416151</v>
       </c>
       <c r="R17">
-        <v>23.9945384432566</v>
+        <v>23.51825490938003</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -3032,143 +3423,143 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D18" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E18" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F18">
-        <v>92.12217479834557</v>
+        <v>91.97177328206851</v>
       </c>
       <c r="G18">
         <v>650</v>
       </c>
       <c r="H18" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I18">
         <v>9.525</v>
       </c>
       <c r="J18" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K18">
         <v>4.865822962046021</v>
       </c>
       <c r="L18">
-        <v>7.333333333333343</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M18">
-        <v>4.556720666666672</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N18">
-        <v>4456799.123767665</v>
+        <v>4530373.771127228</v>
       </c>
       <c r="O18">
-        <v>4284965.648422578</v>
+        <v>4147423.300400615</v>
       </c>
       <c r="P18">
-        <v>10.12569039933982</v>
+        <v>11.57680033084174</v>
       </c>
       <c r="Q18">
-        <v>0.02042811912273964</v>
+        <v>0.02366192227766797</v>
       </c>
       <c r="R18">
-        <v>24.49111394013164</v>
+        <v>24.59987401905227</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="A19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>146</v>
+        <v>188</v>
       </c>
       <c r="C19" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="D19" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="E19" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F19">
-        <v>91.99458901354754</v>
+        <v>91.81548144865465</v>
       </c>
       <c r="G19">
         <v>650</v>
       </c>
       <c r="H19" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I19">
         <v>9.525</v>
       </c>
       <c r="J19" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K19">
         <v>4.865822962046021</v>
       </c>
       <c r="L19">
-        <v>9.333333333333329</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M19">
-        <v>5.799462666666664</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N19">
         <v>4865822.962046022</v>
       </c>
       <c r="O19">
-        <v>4666549.112596197</v>
+        <v>4513236.147443907</v>
       </c>
       <c r="P19">
-        <v>10.12165851845027</v>
+        <v>10.6040190326841</v>
       </c>
       <c r="Q19">
-        <v>0.0203919619810109</v>
+        <v>0.02162439286057684</v>
       </c>
       <c r="R19">
-        <v>23.42623845699047</v>
+        <v>23.56368361565195</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="A20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E20" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F20">
-        <v>91.99458901354735</v>
+        <v>91.81548144865447</v>
       </c>
       <c r="G20">
         <v>650</v>
       </c>
       <c r="H20" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I20">
         <v>9.525</v>
       </c>
       <c r="J20" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K20">
         <v>4.865822962046021</v>
@@ -3180,19 +3571,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N20">
-        <v>4666549.112596197</v>
+        <v>4513236.147443907</v>
       </c>
       <c r="O20">
-        <v>4286663.098591278</v>
+        <v>4130004.625217482</v>
       </c>
       <c r="P20">
-        <v>10.15307222012841</v>
+        <v>11.60655777040942</v>
       </c>
       <c r="Q20">
-        <v>0.02048324471544718</v>
+        <v>0.02372548363882827</v>
       </c>
       <c r="R20">
-        <v>24.48605677657605</v>
+        <v>24.65242534768425</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -3200,31 +3591,31 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C21" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="D21" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="E21" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F21">
-        <v>91.86757273989903</v>
+        <v>91.81548144865461</v>
       </c>
       <c r="G21">
         <v>650</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I21">
         <v>9.525</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K21">
         <v>4.865822962046021</v>
@@ -3236,19 +3627,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N21">
-        <v>4865822.962046022</v>
+        <v>4130004.625217482</v>
       </c>
       <c r="O21">
-        <v>4504532.999528122</v>
+        <v>3706680.759400242</v>
       </c>
       <c r="P21">
-        <v>10.16308893744923</v>
+        <v>12.95011772548902</v>
       </c>
       <c r="Q21">
-        <v>0.02048748515619038</v>
+        <v>0.02654713507203444</v>
       </c>
       <c r="R21">
-        <v>23.8618695178233</v>
+        <v>26.0402285652017</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -3256,31 +3647,31 @@
         <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="D22" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="E22" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F22">
-        <v>91.86757273989903</v>
+        <v>91.54540603453844</v>
       </c>
       <c r="G22">
         <v>650</v>
       </c>
       <c r="H22" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I22">
         <v>9.525</v>
       </c>
       <c r="J22" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K22">
         <v>4.865822962046021</v>
@@ -3292,19 +3683,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N22">
-        <v>4504532.999528122</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O22">
-        <v>4110155.240724877</v>
+        <v>4515346.001689326</v>
       </c>
       <c r="P22">
-        <v>10.19497219015108</v>
+        <v>10.56779621533662</v>
       </c>
       <c r="Q22">
-        <v>0.02058037121995794</v>
+        <v>0.02155023989111336</v>
       </c>
       <c r="R22">
-        <v>25.02779683595519</v>
+        <v>23.55807656442976</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -3312,31 +3703,31 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="C23" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="D23" t="s">
         <v>199</v>
       </c>
       <c r="E23" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F23">
-        <v>91.86757273989903</v>
+        <v>91.54540603453852</v>
       </c>
       <c r="G23">
         <v>650</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I23">
         <v>9.525</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K23">
         <v>4.865822962046021</v>
@@ -3348,19 +3739,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N23">
-        <v>4110155.240724877</v>
+        <v>4515346.001689326</v>
       </c>
       <c r="O23">
-        <v>3671813.6417473</v>
+        <v>4134621.994797298</v>
       </c>
       <c r="P23">
-        <v>10.22715310184007</v>
+        <v>11.55931148812213</v>
       </c>
       <c r="Q23">
-        <v>0.02067641730825224</v>
+        <v>0.02362818251808299</v>
       </c>
       <c r="R23">
-        <v>26.53675764078633</v>
+        <v>24.63846216183151</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -3368,87 +3759,87 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="C24" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="D24" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="E24" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F24">
-        <v>91.57959231714685</v>
+        <v>91.54540603453843</v>
       </c>
       <c r="G24">
         <v>650</v>
       </c>
       <c r="H24" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I24">
         <v>9.525</v>
       </c>
       <c r="J24" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K24">
         <v>4.865822962046021</v>
       </c>
       <c r="L24">
-        <v>16.66666666666666</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M24">
-        <v>10.35618333333333</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N24">
-        <v>4865822.962046022</v>
+        <v>4134621.994797298</v>
       </c>
       <c r="O24">
-        <v>4506841.050669019</v>
+        <v>3714405.889733335</v>
       </c>
       <c r="P24">
-        <v>10.1312303549115</v>
+        <v>12.88492198162437</v>
       </c>
       <c r="Q24">
-        <v>0.0204230830489806</v>
+        <v>0.02641203830764099</v>
       </c>
       <c r="R24">
-        <v>23.85551029457501</v>
+        <v>26.01288437601028</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="A25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="C25" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="E25" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F25">
-        <v>91.57959231714689</v>
+        <v>91.27826336294139</v>
       </c>
       <c r="G25">
         <v>650</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I25">
         <v>9.525</v>
       </c>
       <c r="J25" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K25">
         <v>4.865822962046021</v>
@@ -3460,51 +3851,51 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N25">
-        <v>4506841.050669019</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O25">
-        <v>4115231.692118971</v>
+        <v>4517426.002821975</v>
       </c>
       <c r="P25">
-        <v>10.16301366209049</v>
+        <v>10.53201712106059</v>
       </c>
       <c r="Q25">
-        <v>0.02051546602321178</v>
+        <v>0.02147699767210768</v>
       </c>
       <c r="R25">
-        <v>25.01177295388178</v>
+        <v>23.55255276571357</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="C26" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="D26" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E26" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F26">
-        <v>91.57959231714686</v>
+        <v>91.27826336294127</v>
       </c>
       <c r="G26">
         <v>650</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I26">
         <v>9.525</v>
       </c>
       <c r="J26" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K26">
         <v>4.865822962046021</v>
@@ -3516,19 +3907,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N26">
-        <v>4115231.692118971</v>
+        <v>4517426.002821975</v>
       </c>
       <c r="O26">
-        <v>3680370.06381349</v>
+        <v>4139171.043655685</v>
       </c>
       <c r="P26">
-        <v>10.1950936951748</v>
+        <v>11.51273468820937</v>
       </c>
       <c r="Q26">
-        <v>0.02061096615431796</v>
+        <v>0.0235322660773603</v>
       </c>
       <c r="R26">
-        <v>26.50481489709014</v>
+        <v>24.62472875809429</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -3536,31 +3927,31 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="C27" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E27" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F27">
-        <v>91.29509892413273</v>
+        <v>91.27826336294127</v>
       </c>
       <c r="G27">
         <v>650</v>
       </c>
       <c r="H27" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I27">
         <v>9.525</v>
       </c>
       <c r="J27" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K27">
         <v>4.865822962046021</v>
@@ -3572,19 +3963,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N27">
-        <v>4865822.962046022</v>
+        <v>4139171.043655685</v>
       </c>
       <c r="O27">
-        <v>4509113.018016441</v>
+        <v>3722009.349818648</v>
       </c>
       <c r="P27">
-        <v>10.09975753409903</v>
+        <v>12.82083424510041</v>
       </c>
       <c r="Q27">
-        <v>0.02035946229089909</v>
+        <v>0.02627924927437859</v>
       </c>
       <c r="R27">
-        <v>23.8492554536651</v>
+        <v>25.98605479783625</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -3592,31 +3983,31 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="C28" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="D28" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="E28" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F28">
-        <v>91.29509892413269</v>
+        <v>91.01399329891383</v>
       </c>
       <c r="G28">
         <v>650</v>
       </c>
       <c r="H28" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I28">
         <v>9.525</v>
       </c>
       <c r="J28" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K28">
         <v>4.865822962046021</v>
@@ -3628,19 +4019,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N28">
-        <v>4509113.018016441</v>
+        <v>4865822.962046022</v>
       </c>
       <c r="O28">
-        <v>4120225.047719234</v>
+        <v>4519476.853645065</v>
       </c>
       <c r="P28">
-        <v>10.13144210595202</v>
+        <v>10.4966718062968</v>
       </c>
       <c r="Q28">
-        <v>0.02045134968161054</v>
+        <v>0.02140464575978285</v>
       </c>
       <c r="R28">
-        <v>24.99604135283052</v>
+        <v>23.54711018315774</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -3648,31 +4039,31 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
       <c r="C29" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="D29" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="E29" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F29">
-        <v>91.29509892413263</v>
+        <v>91.01399329891387</v>
       </c>
       <c r="G29">
         <v>650</v>
       </c>
       <c r="H29" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I29">
         <v>9.525</v>
       </c>
       <c r="J29" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K29">
         <v>4.865822962046021</v>
@@ -3684,19 +4075,19 @@
         <v>10.35618333333334</v>
       </c>
       <c r="N29">
-        <v>4120225.047719234</v>
+        <v>4519476.853645065</v>
       </c>
       <c r="O29">
-        <v>3688776.942553297</v>
+        <v>4143653.444823789</v>
       </c>
       <c r="P29">
-        <v>10.16342248192684</v>
+        <v>11.46681052725021</v>
       </c>
       <c r="Q29">
-        <v>0.02054631105651925</v>
+        <v>0.02343769939548617</v>
       </c>
       <c r="R29">
-        <v>26.47354250474622</v>
+        <v>24.61121899911898</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -3704,167 +4095,55 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="C30" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="D30" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="E30" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F30">
-        <v>91.01399329891386</v>
+        <v>91.01399329891382</v>
       </c>
       <c r="G30">
         <v>650</v>
       </c>
       <c r="H30" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="I30">
         <v>9.525</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="K30">
         <v>4.865822962046021</v>
       </c>
       <c r="L30">
-        <v>16.66666666666666</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="M30">
-        <v>10.35618333333333</v>
+        <v>10.35618333333334</v>
       </c>
       <c r="N30">
-        <v>4865822.962046022</v>
+        <v>4143653.444823789</v>
       </c>
       <c r="O30">
-        <v>4511349.999874886</v>
+        <v>3729494.305734892</v>
       </c>
       <c r="P30">
-        <v>10.06865949390148</v>
+        <v>12.7578219864875</v>
       </c>
       <c r="Q30">
-        <v>0.02029660062660992</v>
+        <v>0.0261487000547682</v>
       </c>
       <c r="R30">
-        <v>23.84310173402731</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
-      <c r="A31">
-        <v>3</v>
-      </c>
-      <c r="B31" t="s">
-        <v>158</v>
-      </c>
-      <c r="C31" t="s">
-        <v>189</v>
-      </c>
-      <c r="D31" t="s">
-        <v>190</v>
-      </c>
-      <c r="E31" t="s">
-        <v>203</v>
-      </c>
-      <c r="F31">
-        <v>91.01399329891385</v>
-      </c>
-      <c r="G31">
-        <v>650</v>
-      </c>
-      <c r="H31" t="s">
-        <v>86</v>
-      </c>
-      <c r="I31">
-        <v>9.525</v>
-      </c>
-      <c r="J31" t="s">
-        <v>85</v>
-      </c>
-      <c r="K31">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L31">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M31">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N31">
-        <v>4511349.999874886</v>
-      </c>
-      <c r="O31">
-        <v>4125137.908766091</v>
-      </c>
-      <c r="P31">
-        <v>10.10024650617587</v>
-      </c>
-      <c r="Q31">
-        <v>0.02038799972594251</v>
-      </c>
-      <c r="R31">
-        <v>24.98059228461154</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18">
-      <c r="A32">
-        <v>3</v>
-      </c>
-      <c r="B32" t="s">
-        <v>159</v>
-      </c>
-      <c r="C32" t="s">
-        <v>190</v>
-      </c>
-      <c r="D32" t="s">
-        <v>202</v>
-      </c>
-      <c r="E32" t="s">
-        <v>203</v>
-      </c>
-      <c r="F32">
-        <v>91.0139932989138</v>
-      </c>
-      <c r="G32">
-        <v>650</v>
-      </c>
-      <c r="H32" t="s">
-        <v>86</v>
-      </c>
-      <c r="I32">
-        <v>9.525</v>
-      </c>
-      <c r="J32" t="s">
-        <v>85</v>
-      </c>
-      <c r="K32">
-        <v>4.865822962046021</v>
-      </c>
-      <c r="L32">
-        <v>16.66666666666667</v>
-      </c>
-      <c r="M32">
-        <v>10.35618333333334</v>
-      </c>
-      <c r="N32">
-        <v>4125137.908766091</v>
-      </c>
-      <c r="O32">
-        <v>3697039.184742516</v>
-      </c>
-      <c r="P32">
-        <v>10.1321284117652</v>
-      </c>
-      <c r="Q32">
-        <v>0.02048242939549808</v>
-      </c>
-      <c r="R32">
-        <v>26.4429157419176</v>
+        <v>25.95972429392297</v>
       </c>
     </row>
   </sheetData>
@@ -3874,63 +4153,63 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H1" t="s">
+        <v>219</v>
+      </c>
+      <c r="I1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J1" t="s">
         <v>115</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>215</v>
+      <c r="K1" t="s">
+        <v>221</v>
+      </c>
+      <c r="L1" t="s">
+        <v>121</v>
+      </c>
+      <c r="M1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N1" t="s">
+        <v>223</v>
+      </c>
+      <c r="O1" t="s">
+        <v>224</v>
+      </c>
+      <c r="P1" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>226</v>
+      </c>
+      <c r="R1" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -3938,40 +4217,40 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C2" t="s">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F2">
-        <v>23.33333333333333</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>14.49865666666667</v>
+        <v>21.747985</v>
       </c>
       <c r="H2">
-        <v>1.196598167736171</v>
+        <v>1.338567559469745</v>
       </c>
       <c r="I2">
-        <v>44.16554452507287</v>
+        <v>70.89388840517942</v>
       </c>
       <c r="J2">
-        <v>4.620898857823486</v>
+        <v>7.417399501826221</v>
       </c>
       <c r="K2">
-        <v>6196.717786318451</v>
+        <v>9946.881079938999</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2">
-        <v>4.620898857823486</v>
+        <v>7.417399501826221</v>
       </c>
       <c r="N2">
         <v>0.78</v>
@@ -3980,54 +4259,51 @@
         <v>0.357</v>
       </c>
       <c r="P2">
-        <v>13447784.74391999</v>
+        <v>17660322.29479652</v>
       </c>
       <c r="Q2">
         <v>0</v>
       </c>
       <c r="R2">
-        <v>13447784.74391999</v>
+        <v>17660322.29479652</v>
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3">
-        <v>0</v>
-      </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C3" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="F3">
-        <v>46.66666666666666</v>
+        <v>70</v>
       </c>
       <c r="G3">
-        <v>28.99731333333333</v>
+        <v>43.49597</v>
       </c>
       <c r="H3">
-        <v>1.195601156615998</v>
+        <v>1.335268452481457</v>
       </c>
       <c r="I3">
-        <v>43.86082644500153</v>
+        <v>70.04771970056713</v>
       </c>
       <c r="J3">
-        <v>4.589017185282112</v>
+        <v>7.328867592105301</v>
       </c>
       <c r="K3">
-        <v>6153.963825807017</v>
+        <v>9828.158018365051</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>4.589017185282112</v>
+        <v>12.5</v>
       </c>
       <c r="N3">
         <v>0.78</v>
@@ -4036,51 +4312,54 @@
         <v>0.357</v>
       </c>
       <c r="P3">
-        <v>13400466.03344767</v>
+        <v>0</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R3">
-        <v>13400466.03344767</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="4" spans="1:18">
+      <c r="A4">
+        <v>1</v>
+      </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="D4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E4" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="F4">
-        <v>70</v>
+        <v>102.5</v>
       </c>
       <c r="G4">
-        <v>43.49597</v>
+        <v>63.6905275</v>
       </c>
       <c r="H4">
-        <v>1.194598937317421</v>
+        <v>1.292324273719163</v>
       </c>
       <c r="I4">
-        <v>43.55604290389126</v>
+        <v>50.79133501015063</v>
       </c>
       <c r="J4">
-        <v>4.557128663762801</v>
+        <v>5.314134003317778</v>
       </c>
       <c r="K4">
-        <v>6111.200680679191</v>
+        <v>7126.359981129207</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4">
-        <v>12.5</v>
+        <v>5.314134003317778</v>
       </c>
       <c r="N4">
         <v>0.78</v>
@@ -4089,13 +4368,13 @@
         <v>0.357</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>14480621.70552986</v>
       </c>
       <c r="Q4">
-        <v>16916025.69007904</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>16916025.69007904</v>
+        <v>14480621.70552986</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -4103,40 +4382,40 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F5">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="G5">
-        <v>59.651616</v>
+        <v>83.885085</v>
       </c>
       <c r="H5">
-        <v>1.223843312116393</v>
+        <v>1.174706869887563</v>
       </c>
       <c r="I5">
-        <v>49.69682613490681</v>
+        <v>31.36981453052349</v>
       </c>
       <c r="J5">
-        <v>5.199619060371232</v>
+        <v>3.282122788091933</v>
       </c>
       <c r="K5">
-        <v>6972.793152339029</v>
+        <v>4401.392301287044</v>
       </c>
       <c r="L5">
         <v>0</v>
       </c>
       <c r="M5">
-        <v>5.199619060371232</v>
+        <v>3.282122788091933</v>
       </c>
       <c r="N5">
         <v>0.78</v>
@@ -4145,13 +4424,13 @@
         <v>0.357</v>
       </c>
       <c r="P5">
-        <v>14309488.92802266</v>
+        <v>11474485.84564348</v>
       </c>
       <c r="Q5">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>14309488.92802266</v>
+        <v>11474485.84564348</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -4159,40 +4438,40 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="E6" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F6">
-        <v>122</v>
+        <v>167.5</v>
       </c>
       <c r="G6">
-        <v>75.80726200000001</v>
+        <v>104.0796425</v>
       </c>
       <c r="H6">
-        <v>1.153166220920455</v>
+        <v>1.173957721893576</v>
       </c>
       <c r="I6">
-        <v>28.40604334386236</v>
+        <v>31.18908179636074</v>
       </c>
       <c r="J6">
-        <v>2.972032942295563</v>
+        <v>3.263213303473446</v>
       </c>
       <c r="K6">
-        <v>3985.555616277196</v>
+        <v>4376.034304223961</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2.972032942295563</v>
+        <v>3.263213303473446</v>
       </c>
       <c r="N6">
         <v>0.78</v>
@@ -4201,54 +4480,51 @@
         <v>0.357</v>
       </c>
       <c r="P6">
-        <v>11021433.00223319</v>
+        <v>11446815.23847485</v>
       </c>
       <c r="Q6">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>11021433.00223319</v>
+        <v>11446815.23847485</v>
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7">
-        <v>1</v>
-      </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="E7" t="s">
-        <v>216</v>
+        <v>150</v>
       </c>
       <c r="F7">
-        <v>148</v>
+        <v>200</v>
       </c>
       <c r="G7">
-        <v>91.96290800000001</v>
+        <v>124.2742</v>
       </c>
       <c r="H7">
-        <v>1.136003719824769</v>
+        <v>1.173215900478742</v>
       </c>
       <c r="I7">
-        <v>25.42742033087925</v>
+        <v>31.01027450513704</v>
       </c>
       <c r="J7">
-        <v>2.660389197684499</v>
+        <v>3.244505271756164</v>
       </c>
       <c r="K7">
-        <v>3567.635121878867</v>
+        <v>4350.946459530451</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>2.660389197684499</v>
+        <v>12.5</v>
       </c>
       <c r="N7">
         <v>0.78</v>
@@ -4257,54 +4533,54 @@
         <v>0.357</v>
       </c>
       <c r="P7">
-        <v>10567628.10021256</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>16916025.69007904</v>
       </c>
       <c r="R7">
-        <v>10567628.10021256</v>
+        <v>16916025.69007904</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D8" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="E8" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F8">
-        <v>174</v>
+        <v>250</v>
       </c>
       <c r="G8">
-        <v>108.118554</v>
+        <v>155.34275</v>
       </c>
       <c r="H8">
-        <v>1.135557052560567</v>
+        <v>1.312717031189202</v>
       </c>
       <c r="I8">
-        <v>25.31463175758476</v>
+        <v>53.58637457851545</v>
       </c>
       <c r="J8">
-        <v>2.64858849206394</v>
+        <v>5.606570002645178</v>
       </c>
       <c r="K8">
-        <v>3551.810139627585</v>
+        <v>7518.522504947236</v>
       </c>
       <c r="L8">
         <v>0</v>
       </c>
       <c r="M8">
-        <v>2.64858849206394</v>
+        <v>5.606570002645178</v>
       </c>
       <c r="N8">
         <v>0.78</v>
@@ -4313,45 +4589,45 @@
         <v>0.357</v>
       </c>
       <c r="P8">
-        <v>10550474.22654086</v>
+        <v>14918574.77541785</v>
       </c>
       <c r="Q8">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>10550474.22654086</v>
+        <v>14918574.77541785</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="B9" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D9" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="E9" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F9">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G9">
-        <v>124.2742</v>
+        <v>186.4113</v>
       </c>
       <c r="H9">
-        <v>1.135107390092091</v>
+        <v>1.309986874481117</v>
       </c>
       <c r="I9">
-        <v>25.20163354951717</v>
+        <v>53.00448140737202</v>
       </c>
       <c r="J9">
-        <v>2.636765853031398</v>
+        <v>5.545688391904807</v>
       </c>
       <c r="K9">
-        <v>3535.955744232165</v>
+        <v>7436.879047312184</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -4377,43 +4653,43 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="D10" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="E10" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F10">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="G10">
-        <v>155.34275</v>
+        <v>217.47985</v>
       </c>
       <c r="H10">
-        <v>1.325182440285976</v>
+        <v>1.307310784236236</v>
       </c>
       <c r="I10">
-        <v>57.13895452268778</v>
+        <v>52.434519770003</v>
       </c>
       <c r="J10">
-        <v>5.97826501473844</v>
+        <v>5.486055139163487</v>
       </c>
       <c r="K10">
-        <v>8016.972950064543</v>
+        <v>7356.909662721019</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>5.97826501473844</v>
+        <v>5.486055139163487</v>
       </c>
       <c r="N10">
         <v>0.78</v>
@@ -4422,122 +4698,13 @@
         <v>0.357</v>
       </c>
       <c r="P10">
-        <v>15477160.67336135</v>
+        <v>14737928.98901344</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>15477160.67336135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="B11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" t="s">
-        <v>200</v>
-      </c>
-      <c r="D11" t="s">
-        <v>185</v>
-      </c>
-      <c r="E11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F11">
-        <v>300.0000000000001</v>
-      </c>
-      <c r="G11">
-        <v>186.4113</v>
-      </c>
-      <c r="H11">
-        <v>1.322101548941576</v>
-      </c>
-      <c r="I11">
-        <v>56.44708376384304</v>
-      </c>
-      <c r="J11">
-        <v>5.905876802758123</v>
-      </c>
-      <c r="K11">
-        <v>7919.898910034698</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>12.5</v>
-      </c>
-      <c r="N11">
-        <v>0.78</v>
-      </c>
-      <c r="O11">
-        <v>0.357</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>16916025.69007904</v>
-      </c>
-      <c r="R11">
-        <v>16916025.69007904</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E12" t="s">
-        <v>216</v>
-      </c>
-      <c r="F12">
-        <v>350.0000000000001</v>
-      </c>
-      <c r="G12">
-        <v>217.47985</v>
-      </c>
-      <c r="H12">
-        <v>1.319088423567839</v>
-      </c>
-      <c r="I12">
-        <v>55.77490782861931</v>
-      </c>
-      <c r="J12">
-        <v>5.83554919682159</v>
-      </c>
-      <c r="K12">
-        <v>7825.588183921689</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>5.83554919682159</v>
-      </c>
-      <c r="N12">
-        <v>0.78</v>
-      </c>
-      <c r="O12">
-        <v>0.357</v>
-      </c>
-      <c r="P12">
-        <v>15262430.26759074</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>15262430.26759074</v>
+        <v>14737928.98901344</v>
       </c>
     </row>
   </sheetData>
@@ -4547,20 +4714,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>218</v>
+      <c r="A1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B2">
         <v>4865822.962046022</v>
@@ -4568,82 +4735,82 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B3">
-        <v>4427462.918581173</v>
+        <v>4438116.177952614</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>152</v>
       </c>
       <c r="B4">
-        <v>4066380.087520617</v>
+        <v>3963528.099593595</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B5">
-        <v>4865822.962046022</v>
+        <v>3635097.03161606</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B6">
-        <v>4760595.472101057</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B7">
-        <v>4312888.561809869</v>
+        <v>4711069.308999785</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="B8">
-        <v>4069771.039548116</v>
+        <v>4212053.220545113</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B9">
-        <v>4865822.962046022</v>
+        <v>3644078.427078389</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B10">
-        <v>4599097.546686064</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="B11">
-        <v>4073185.409801771</v>
+        <v>4362643.803546251</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B12">
-        <v>4865822.962046022</v>
+        <v>3791934.656830566</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4651,76 +4818,76 @@
         <v>168</v>
       </c>
       <c r="B13">
-        <v>4349434.559984447</v>
+        <v>3765171.838831699</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B14">
-        <v>3975854.518199351</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B15">
-        <v>4865822.962046022</v>
+        <v>4542771.487687924</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B16">
-        <v>4693014.32323207</v>
+        <v>4170354.630079336</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B17">
-        <v>4324128.083916678</v>
+        <v>4142159.279711842</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B18">
-        <v>4219533.033288239</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B19">
-        <v>4865822.962046022</v>
+        <v>4547558.708764091</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B20">
-        <v>4610217.933448978</v>
+        <v>4164881.467165636</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B21">
-        <v>4283280.835380175</v>
+        <v>4144802.552341937</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B22">
         <v>4865822.962046022</v>
@@ -4728,87 +4895,87 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="B23">
-        <v>4823729.897071396</v>
+        <v>4530373.771127228</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B24">
-        <v>4456799.123767665</v>
+        <v>4147423.300400615</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B25">
-        <v>4284965.648422578</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="B26">
-        <v>4865822.962046022</v>
+        <v>4513236.147443907</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B27">
-        <v>4666549.112596197</v>
+        <v>4130004.625217482</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B28">
-        <v>4286663.098591278</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B29">
-        <v>4865822.962046022</v>
+        <v>3706680.759400242</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="B30">
-        <v>4504532.999528122</v>
+        <v>4515346.001689326</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B31">
-        <v>4110155.240724877</v>
+        <v>4134621.994797298</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B32">
-        <v>3671813.6417473</v>
+        <v>3714405.889733335</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="B33">
         <v>4865822.962046022</v>
@@ -4816,90 +4983,58 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="B34">
-        <v>4506841.050669019</v>
+        <v>4517426.002821975</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="B35">
-        <v>4115231.692118971</v>
+        <v>4139171.043655685</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B36">
-        <v>3680370.06381349</v>
+        <v>4865822.962046022</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="B37">
-        <v>4865822.962046022</v>
+        <v>3722009.349818648</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="B38">
-        <v>4509113.018016441</v>
+        <v>4519476.853645065</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="B39">
-        <v>4120225.047719234</v>
+        <v>4143653.444823789</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B40">
-        <v>3688776.942553297</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>188</v>
-      </c>
-      <c r="B41">
-        <v>4865822.962046022</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>189</v>
-      </c>
-      <c r="B42">
-        <v>4511349.999874886</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>190</v>
-      </c>
-      <c r="B43">
-        <v>4125137.908766091</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>202</v>
-      </c>
-      <c r="B44">
-        <v>3697039.184742516</v>
+        <v>3729494.305734892</v>
       </c>
     </row>
   </sheetData>
@@ -4913,37 +5048,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>225</v>
+      <c r="A1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G1" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B2">
         <v>19.78565086669546</v>
       </c>
       <c r="C2">
-        <v>19.7856508665618</v>
+        <v>19.78565087622836</v>
       </c>
       <c r="D2">
         <v>58.14923187271204</v>
@@ -4952,15 +5087,15 @@
         <v>1150.5204</v>
       </c>
       <c r="F2">
-        <v>1150.520399992228</v>
+        <v>1150.520400554331</v>
       </c>
       <c r="G2">
-        <v>-6.755590080814732E-10</v>
+        <v>4.818087994821781E-08</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="B3">
         <v>51.44269156552292</v>
@@ -4983,7 +5118,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B4">
         <v>39.57130173339092</v>
@@ -5002,6 +5137,839 @@
       </c>
       <c r="G4">
         <v>-3.591202233109923E-14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" t="s">
+        <v>253</v>
+      </c>
+      <c r="F7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G7" t="s">
+        <v>253</v>
+      </c>
+      <c r="H7" t="s">
+        <v>256</v>
+      </c>
+      <c r="I7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B8" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G8" t="s">
+        <v>263</v>
+      </c>
+      <c r="H8" t="s">
+        <v>264</v>
+      </c>
+      <c r="I8" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E9" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" t="s">
+        <v>256</v>
+      </c>
+      <c r="G9" t="s">
+        <v>244</v>
+      </c>
+      <c r="H9" t="s">
+        <v>268</v>
+      </c>
+      <c r="I9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C10" t="s">
+        <v>253</v>
+      </c>
+      <c r="D10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E10" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B12" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>273</v>
+      </c>
+      <c r="B13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" t="s">
+        <v>264</v>
+      </c>
+      <c r="E13" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>274</v>
+      </c>
+      <c r="B14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D14" t="s">
+        <v>275</v>
+      </c>
+      <c r="E14" t="s">
+        <v>253</v>
+      </c>
+      <c r="F14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G14" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C15" t="s">
+        <v>253</v>
+      </c>
+      <c r="D15" t="s">
+        <v>264</v>
+      </c>
+      <c r="E15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C16" t="s">
+        <v>253</v>
+      </c>
+      <c r="D16" t="s">
+        <v>264</v>
+      </c>
+      <c r="E16" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>278</v>
+      </c>
+      <c r="B17" t="s">
+        <v>267</v>
+      </c>
+      <c r="C17" t="s">
+        <v>253</v>
+      </c>
+      <c r="D17" t="s">
+        <v>264</v>
+      </c>
+      <c r="E17" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B18" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>280</v>
+      </c>
+      <c r="B19" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>281</v>
+      </c>
+      <c r="B20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" t="s">
+        <v>253</v>
+      </c>
+      <c r="D20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E20" t="s">
+        <v>283</v>
+      </c>
+      <c r="F20" t="s">
+        <v>284</v>
+      </c>
+      <c r="G20" t="s">
+        <v>285</v>
+      </c>
+      <c r="H20" t="s">
+        <v>286</v>
+      </c>
+      <c r="I20" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>287</v>
+      </c>
+      <c r="B21" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" t="s">
+        <v>253</v>
+      </c>
+      <c r="D21" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" t="s">
+        <v>288</v>
+      </c>
+      <c r="F21" t="s">
+        <v>284</v>
+      </c>
+      <c r="G21" t="s">
+        <v>285</v>
+      </c>
+      <c r="H21" t="s">
+        <v>286</v>
+      </c>
+      <c r="I21" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>289</v>
+      </c>
+      <c r="B22" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>291</v>
+      </c>
+      <c r="B23" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>293</v>
+      </c>
+      <c r="B24" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>294</v>
+      </c>
+      <c r="B25" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>296</v>
+      </c>
+      <c r="B26" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>297</v>
+      </c>
+      <c r="B27" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>298</v>
+      </c>
+      <c r="B28" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>299</v>
+      </c>
+      <c r="B29" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>301</v>
+      </c>
+      <c r="B30" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>303</v>
+      </c>
+      <c r="B31" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>305</v>
+      </c>
+      <c r="B32" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>307</v>
+      </c>
+      <c r="B33" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>308</v>
+      </c>
+      <c r="B34" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>309</v>
+      </c>
+      <c r="B35" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>311</v>
+      </c>
+      <c r="B36" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>313</v>
+      </c>
+      <c r="B37" t="s">
+        <v>314</v>
+      </c>
+      <c r="C37" t="s">
+        <v>244</v>
+      </c>
+      <c r="D37" t="s">
+        <v>315</v>
+      </c>
+      <c r="E37" t="s">
+        <v>283</v>
+      </c>
+      <c r="F37" t="s">
+        <v>316</v>
+      </c>
+      <c r="G37" t="s">
+        <v>248</v>
+      </c>
+      <c r="H37" t="s">
+        <v>317</v>
+      </c>
+      <c r="I37" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>319</v>
+      </c>
+      <c r="B38" t="s">
+        <v>314</v>
+      </c>
+      <c r="C38" t="s">
+        <v>320</v>
+      </c>
+      <c r="D38" t="s">
+        <v>315</v>
+      </c>
+      <c r="E38" t="s">
+        <v>283</v>
+      </c>
+      <c r="F38" t="s">
+        <v>316</v>
+      </c>
+      <c r="G38" t="s">
+        <v>248</v>
+      </c>
+      <c r="H38" t="s">
+        <v>317</v>
+      </c>
+      <c r="I38" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>321</v>
+      </c>
+      <c r="B39" t="s">
+        <v>314</v>
+      </c>
+      <c r="C39" t="s">
+        <v>322</v>
+      </c>
+      <c r="D39" t="s">
+        <v>315</v>
+      </c>
+      <c r="E39" t="s">
+        <v>283</v>
+      </c>
+      <c r="F39" t="s">
+        <v>316</v>
+      </c>
+      <c r="G39" t="s">
+        <v>248</v>
+      </c>
+      <c r="H39" t="s">
+        <v>317</v>
+      </c>
+      <c r="I39" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>323</v>
+      </c>
+      <c r="B40" t="s">
+        <v>314</v>
+      </c>
+      <c r="C40" t="s">
+        <v>244</v>
+      </c>
+      <c r="D40" t="s">
+        <v>315</v>
+      </c>
+      <c r="E40" t="s">
+        <v>283</v>
+      </c>
+      <c r="F40" t="s">
+        <v>316</v>
+      </c>
+      <c r="G40" t="s">
+        <v>248</v>
+      </c>
+      <c r="H40" t="s">
+        <v>317</v>
+      </c>
+      <c r="I40" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>324</v>
+      </c>
+      <c r="B41" t="s">
+        <v>314</v>
+      </c>
+      <c r="C41" t="s">
+        <v>325</v>
+      </c>
+      <c r="D41" t="s">
+        <v>315</v>
+      </c>
+      <c r="E41" t="s">
+        <v>283</v>
+      </c>
+      <c r="F41" t="s">
+        <v>316</v>
+      </c>
+      <c r="G41" t="s">
+        <v>248</v>
+      </c>
+      <c r="H41" t="s">
+        <v>317</v>
+      </c>
+      <c r="I41" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>326</v>
+      </c>
+      <c r="B42" t="s">
+        <v>314</v>
+      </c>
+      <c r="C42" t="s">
+        <v>327</v>
+      </c>
+      <c r="D42" t="s">
+        <v>315</v>
+      </c>
+      <c r="E42" t="s">
+        <v>283</v>
+      </c>
+      <c r="F42" t="s">
+        <v>316</v>
+      </c>
+      <c r="G42" t="s">
+        <v>248</v>
+      </c>
+      <c r="H42" t="s">
+        <v>317</v>
+      </c>
+      <c r="I42" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>328</v>
+      </c>
+      <c r="B43" t="s">
+        <v>314</v>
+      </c>
+      <c r="C43" t="s">
+        <v>253</v>
+      </c>
+      <c r="D43" t="s">
+        <v>315</v>
+      </c>
+      <c r="E43" t="s">
+        <v>283</v>
+      </c>
+      <c r="F43" t="s">
+        <v>316</v>
+      </c>
+      <c r="G43" t="s">
+        <v>248</v>
+      </c>
+      <c r="H43" t="s">
+        <v>317</v>
+      </c>
+      <c r="I43" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>314</v>
+      </c>
+      <c r="C44" t="s">
+        <v>244</v>
+      </c>
+      <c r="D44" t="s">
+        <v>315</v>
+      </c>
+      <c r="E44" t="s">
+        <v>283</v>
+      </c>
+      <c r="F44" t="s">
+        <v>316</v>
+      </c>
+      <c r="G44" t="s">
+        <v>248</v>
+      </c>
+      <c r="H44" t="s">
+        <v>317</v>
+      </c>
+      <c r="I44" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>329</v>
+      </c>
+      <c r="B45" t="s">
+        <v>314</v>
+      </c>
+      <c r="C45" t="s">
+        <v>244</v>
+      </c>
+      <c r="D45" t="s">
+        <v>315</v>
+      </c>
+      <c r="E45" t="s">
+        <v>283</v>
+      </c>
+      <c r="F45" t="s">
+        <v>316</v>
+      </c>
+      <c r="G45" t="s">
+        <v>248</v>
+      </c>
+      <c r="H45" t="s">
+        <v>317</v>
+      </c>
+      <c r="I45" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>330</v>
+      </c>
+      <c r="B46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C46" t="s">
+        <v>331</v>
+      </c>
+      <c r="D46" t="s">
+        <v>332</v>
+      </c>
+      <c r="E46" t="s">
+        <v>333</v>
+      </c>
+      <c r="F46" t="s">
+        <v>264</v>
+      </c>
+      <c r="G46" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>334</v>
+      </c>
+      <c r="B47" t="s">
+        <v>314</v>
+      </c>
+      <c r="C47" t="s">
+        <v>302</v>
+      </c>
+      <c r="D47" t="s">
+        <v>332</v>
+      </c>
+      <c r="E47" t="s">
+        <v>253</v>
+      </c>
+      <c r="F47" t="s">
+        <v>264</v>
+      </c>
+      <c r="G47" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>335</v>
+      </c>
+      <c r="B48" t="s">
+        <v>314</v>
+      </c>
+      <c r="C48" t="s">
+        <v>302</v>
+      </c>
+      <c r="D48" t="s">
+        <v>332</v>
+      </c>
+      <c r="E48" t="s">
+        <v>253</v>
+      </c>
+      <c r="F48" t="s">
+        <v>264</v>
+      </c>
+      <c r="G48" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>336</v>
+      </c>
+      <c r="B49" t="s">
+        <v>314</v>
+      </c>
+      <c r="C49" t="s">
+        <v>331</v>
+      </c>
+      <c r="D49" t="s">
+        <v>332</v>
+      </c>
+      <c r="E49" t="s">
+        <v>253</v>
+      </c>
+      <c r="F49" t="s">
+        <v>264</v>
+      </c>
+      <c r="G49" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>337</v>
+      </c>
+      <c r="B50" t="s">
+        <v>314</v>
+      </c>
+      <c r="C50" t="s">
+        <v>338</v>
+      </c>
+      <c r="D50" t="s">
+        <v>264</v>
+      </c>
+      <c r="E50" t="s">
+        <v>265</v>
       </c>
     </row>
   </sheetData>
